--- a/Employee_Reports_wi52/Rommel Tamayo Eleosida Q0540.xlsx
+++ b/Employee_Reports_wi52/Rommel Tamayo Eleosida Q0540.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,12 +54,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
-        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -93,9 +87,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -475,7 +466,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -578,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -762,11 +753,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -799,11 +790,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -836,11 +827,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -873,11 +864,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -922,11 +913,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -971,11 +962,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1020,11 +1011,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1069,11 +1060,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-49</v>
+        <v>-57</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1118,11 +1109,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-49</v>
+        <v>-57</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1167,11 +1158,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1216,11 +1207,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1265,11 +1256,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1314,11 +1305,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1363,11 +1354,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1412,11 +1403,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1461,11 +1452,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1510,11 +1501,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1559,11 +1550,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1608,11 +1599,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1645,11 +1636,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1694,11 +1685,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1743,11 +1734,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1780,11 +1771,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1829,11 +1820,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1878,11 +1869,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1927,11 +1918,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1976,11 +1967,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2025,11 +2016,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2074,11 +2065,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2123,11 +2114,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2172,11 +2163,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2209,11 +2200,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2258,11 +2249,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2295,11 +2286,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2344,11 +2335,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2359,41 +2350,41 @@
       <c r="K41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr"/>
-      <c r="D42" s="5" t="inlineStr"/>
-      <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>01-Sep-2024</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>01-Sep-2026</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>23-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3025,7 +3016,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7527</v>
+        <v>7519</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3054,7 +3045,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3083,7 +3074,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3112,7 +3103,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3141,7 +3132,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3170,7 +3161,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3199,7 +3190,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7961</v>
+        <v>7953</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3294,7 +3285,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3323,7 +3314,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3352,7 +3343,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3381,7 +3372,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3410,7 +3401,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3439,7 +3430,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3468,7 +3459,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3497,7 +3488,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3526,7 +3517,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3555,7 +3546,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3584,7 +3575,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3613,7 +3604,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -3642,7 +3633,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3671,7 +3662,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3700,7 +3691,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3729,7 +3720,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3758,7 +3749,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3787,7 +3778,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -3816,7 +3807,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7933</v>
+        <v>7925</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3836,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -3874,7 +3865,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7913</v>
+        <v>7905</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
